--- a/artfynd/A 59717-2022 artfynd.xlsx
+++ b/artfynd/A 59717-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124019299</v>
+        <v>124019297</v>
       </c>
       <c r="B2" t="n">
-        <v>58033</v>
+        <v>56943</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124019297</v>
+        <v>124019299</v>
       </c>
       <c r="B3" t="n">
-        <v>56943</v>
+        <v>58033</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/artfynd/A 59717-2022 artfynd.xlsx
+++ b/artfynd/A 59717-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124019297</v>
+        <v>124019299</v>
       </c>
       <c r="B2" t="n">
-        <v>56943</v>
+        <v>58033</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124019299</v>
+        <v>124019297</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>56943</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/artfynd/A 59717-2022 artfynd.xlsx
+++ b/artfynd/A 59717-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124019297</v>
+        <v>124019299</v>
       </c>
       <c r="B2" t="n">
-        <v>56965</v>
+        <v>58055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124019299</v>
+        <v>124019297</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>56965</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/artfynd/A 59717-2022 artfynd.xlsx
+++ b/artfynd/A 59717-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124019299</v>
+        <v>124019297</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
+        <v>56965</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124019297</v>
+        <v>124019299</v>
       </c>
       <c r="B3" t="n">
-        <v>56965</v>
+        <v>58055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
